--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487583_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487583_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3937</v>
+        <v>1.5919</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5043</v>
+        <v>3.755</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1106</v>
+        <v>-2.1631</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4423</v>
+        <v>-1.2245</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9056</v>
+        <v>-2.755</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4633</v>
+        <v>1.5305</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3201</v>
+        <v>2.5721</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2161</v>
+        <v>0.758</v>
       </c>
       <c r="L2" t="n">
-        <v>0.104</v>
+        <v>1.8141</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.8778</v>
+        <v>-3.7966</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.3105</v>
+        <v>-3.513</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5673</v>
+        <v>-0.2836</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9105</v>
+        <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9035</v>
+        <v>-0.3477</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0946</v>
+        <v>-0.041</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8089</v>
+        <v>-0.3067</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0478</v>
+        <v>1.2239</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8909</v>
+        <v>1.4905</v>
       </c>
       <c r="E3" t="n">
-        <v>4.992</v>
+        <v>4.5916</v>
       </c>
       <c r="F3" t="n">
         <v>-3.1011</v>
@@ -688,10 +688,10 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5698</v>
+        <v>-0.9702</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1233</v>
+        <v>-0.2771</v>
       </c>
       <c r="U3" t="n">
         <v>-0.6931</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2555</v>
+        <v>1.2658</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5548</v>
+        <v>3.3031</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2993</v>
+        <v>-2.0373</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2245</v>
+        <v>1.4423</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.755</v>
+        <v>1.9056</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5305</v>
+        <v>-0.4633</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5721</v>
+        <v>6.3201</v>
       </c>
       <c r="K4" t="n">
-        <v>0.758</v>
+        <v>6.2161</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8141</v>
+        <v>0.104</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.7966</v>
+        <v>-4.8778</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.513</v>
+        <v>-4.3105</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2836</v>
+        <v>-0.5673</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9403</v>
+        <v>2.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6842</v>
+        <v>-0.2243</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2412</v>
+        <v>-0.1066</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.443</v>
+        <v>-0.1177</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2239</v>
+        <v>0.0478</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0321</v>
+        <v>-0.8409</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2176</v>
+        <v>0.5179</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2498</v>
+        <v>-1.3588</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6526999999999999</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.6822</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6057</v>
+        <v>-0.3054</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2678</v>
+        <v>-0.3768</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2821</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.497</v>
+        <v>-1.7366</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0919</v>
+        <v>2.0526</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.589</v>
+        <v>-3.7892</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5786</v>
+        <v>-4.0815</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2894</v>
+        <v>-1.6568</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2892</v>
+        <v>-2.4247</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3845</v>
+        <v>0.2394</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2399</v>
+        <v>2.0968</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1446</v>
+        <v>-1.8574</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9631</v>
+        <v>-4.3209</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5293</v>
+        <v>-3.7536</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4338</v>
+        <v>-0.5673</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8006</v>
+        <v>-1.6372</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6046</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.196</v>
+        <v>-1.1266</v>
       </c>
       <c r="V6" t="n">
+        <v>3.0119</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="X6" t="n">
         <v>-0.2821</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.5642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5191</v>
+        <v>-1.9425</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3519</v>
+        <v>0.2921</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.871</v>
+        <v>-2.2346</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0815</v>
+        <v>-1.5786</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6568</v>
+        <v>-1.2894</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4247</v>
+        <v>-0.2892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2394</v>
+        <v>1.3845</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0968</v>
+        <v>1.2399</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8574</v>
+        <v>0.1446</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.3209</v>
+        <v>-2.9631</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.7536</v>
+        <v>-2.5293</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5673</v>
+        <v>-0.4338</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4197</v>
+        <v>-1.2461</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2113</v>
+        <v>-0.4044</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2084</v>
+        <v>-0.8417</v>
       </c>
       <c r="V7" t="n">
-        <v>3.0119</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>3.294</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1491</v>
+        <v>-4.4578</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8461</v>
+        <v>1.3466</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.9952</v>
+        <v>-5.8044</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8201</v>
@@ -1156,13 +1156,13 @@
         <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5215</v>
+        <v>-0.8303</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8479</v>
+        <v>-0.3474</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6736</v>
+        <v>-0.4828</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5537</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2586</v>
+        <v>-5.2864</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1185</v>
+        <v>-3.4188</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1401</v>
+        <v>-1.8675</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0362</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5821</v>
+        <v>-0.6098</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3039</v>
+        <v>0.0036</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.886</v>
+        <v>-0.6135</v>
       </c>
       <c r="V10" t="n">
         <v>-1.506</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.0185</v>
+        <v>-13.0187</v>
       </c>
       <c r="E11" t="n">
         <v>11.5911</v>
       </c>
       <c r="F11" t="n">
-        <v>-24.6098</v>
+        <v>-24.6097</v>
       </c>
       <c r="G11" t="n">
         <v>-14.5774</v>
@@ -1303,7 +1303,7 @@
         <v>-2.8642</v>
       </c>
       <c r="P11" t="n">
-        <v>4.850800000000001</v>
+        <v>4.8508</v>
       </c>
       <c r="Q11" t="n">
         <v>-9.701699999999999</v>
@@ -1312,16 +1312,16 @@
         <v>14.5524</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.7296</v>
+        <v>-6.7295</v>
       </c>
       <c r="T11" t="n">
         <v>-2.1706</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.559</v>
+        <v>-4.5589</v>
       </c>
       <c r="V11" t="n">
-        <v>3.437299999999999</v>
+        <v>3.4373</v>
       </c>
       <c r="W11" t="n">
         <v>11.2015</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.7864</v>
+        <v>5.7041</v>
       </c>
       <c r="E12" t="n">
-        <v>8.351000000000001</v>
+        <v>8.050700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5647</v>
+        <v>-2.3466</v>
       </c>
       <c r="G12" t="n">
         <v>2.7748</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9832</v>
+        <v>0.9009</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3358</v>
+        <v>1.0355</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3526</v>
+        <v>-0.1346</v>
       </c>
       <c r="V12" t="n">
         <v>0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2498</v>
+        <v>4.1948</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4571</v>
+        <v>1.7564</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7928</v>
+        <v>2.4385</v>
       </c>
       <c r="G13" t="n">
         <v>3.2468</v>
@@ -1468,13 +1468,13 @@
         <v>0.194</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0911</v>
+        <v>1.0361</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9107</v>
+        <v>0.21</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1804</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2821</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0188</v>
+        <v>2.8552</v>
       </c>
       <c r="E14" t="n">
         <v>4.6027</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5839</v>
+        <v>-1.7475</v>
       </c>
       <c r="G14" t="n">
         <v>6.045</v>
@@ -1546,13 +1546,13 @@
         <v>0.5821</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6783</v>
+        <v>0.5148</v>
       </c>
       <c r="T14" t="n">
         <v>0.2434</v>
       </c>
       <c r="U14" t="n">
-        <v>0.435</v>
+        <v>0.2714</v>
       </c>
       <c r="V14" t="n">
         <v>0.5642</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5111</v>
+        <v>2.27</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4115</v>
+        <v>5.3079</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9004</v>
+        <v>-3.0379</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3559</v>
+        <v>3.8281</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4844</v>
+        <v>5.8874</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8403</v>
+        <v>-2.0593</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2886</v>
+        <v>5.9618</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1668</v>
+        <v>7.8597</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1218</v>
+        <v>-1.898</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6445</v>
+        <v>-2.1337</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6824</v>
+        <v>-1.9724</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9621</v>
+        <v>-0.1613</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
         <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7775</v>
+        <v>0.1419</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2454</v>
+        <v>0.3163</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5321</v>
+        <v>-0.1744</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2239</v>
+        <v>-1.506</v>
       </c>
       <c r="W15" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5642</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1149</v>
+        <v>1.6911</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5071</v>
+        <v>0.8969</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3922</v>
+        <v>0.7942</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8281</v>
+        <v>-0.256</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8874</v>
+        <v>-0.767</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0593</v>
+        <v>0.511</v>
       </c>
       <c r="J16" t="n">
-        <v>5.9618</v>
+        <v>0.4802</v>
       </c>
       <c r="K16" t="n">
-        <v>7.8597</v>
+        <v>0.3584</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.898</v>
+        <v>0.1218</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1337</v>
+        <v>-0.7362</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9724</v>
+        <v>-1.1254</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1613</v>
+        <v>0.3893</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0132</v>
+        <v>0.5008</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4845</v>
+        <v>0.1346</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5286999999999999</v>
+        <v>0.3662</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0024</v>
+        <v>1.1664</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.3921</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9105</v>
+        <v>0.7743</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5905</v>
@@ -1780,13 +1780,13 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>0.175</v>
+        <v>0.339</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2423</v>
+        <v>0.058</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4172</v>
+        <v>0.281</v>
       </c>
       <c r="V17" t="n">
         <v>1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5934</v>
+        <v>0.877</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1479</v>
+        <v>2.4529</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4455</v>
+        <v>-1.5759</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4592</v>
+        <v>2.4794</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14</v>
+        <v>-1.7482</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3192</v>
+        <v>4.2276</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9583</v>
+        <v>4.0769</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8949</v>
+        <v>-0.8403</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0634</v>
+        <v>4.9172</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4991</v>
+        <v>-1.5975</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7549</v>
+        <v>-0.9079</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2558</v>
+        <v>-0.6896</v>
       </c>
       <c r="P18" t="n">
         <v>-0.7761</v>
@@ -1858,28 +1858,28 @@
         <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>1.57</v>
+        <v>0.3976</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7896</v>
+        <v>0.3163</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7804</v>
+        <v>0.0813</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6597</v>
+        <v>-1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5905</v>
+        <v>0.0919</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0961</v>
+        <v>2.2103</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4944</v>
+        <v>-2.1184</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.256</v>
+        <v>-0.3559</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.767</v>
+        <v>0.4844</v>
       </c>
       <c r="I19" t="n">
-        <v>0.511</v>
+        <v>-0.8403</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4802</v>
+        <v>2.2886</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3584</v>
+        <v>2.1668</v>
       </c>
       <c r="L19" t="n">
         <v>0.1218</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7362</v>
+        <v>-2.6445</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1254</v>
+        <v>-1.6824</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3893</v>
+        <v>-0.9621</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5998</v>
+        <v>1.3582</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6662</v>
+        <v>1.0442</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0664</v>
+        <v>0.3141</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>1.788</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0489</v>
+        <v>-0.1068</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6521</v>
+        <v>-0.2525</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6031</v>
+        <v>0.1457</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4794</v>
+        <v>0.4592</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7482</v>
+        <v>0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2276</v>
+        <v>0.3192</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0769</v>
+        <v>1.9583</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8403</v>
+        <v>1.8949</v>
       </c>
       <c r="L20" t="n">
-        <v>4.9172</v>
+        <v>0.0634</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5975</v>
+        <v>-1.4991</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9079</v>
+        <v>-1.7549</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6896</v>
+        <v>0.2558</v>
       </c>
       <c r="P20" t="n">
         <v>-0.7761</v>
@@ -2014,22 +2014,22 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4305</v>
+        <v>0.8698</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4845</v>
+        <v>0.3892</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0541</v>
+        <v>0.4806</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5664</v>
+        <v>-2.3127</v>
       </c>
       <c r="E21" t="n">
-        <v>3.0866</v>
+        <v>2.2858</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.6529</v>
+        <v>-4.5984</v>
       </c>
       <c r="G21" t="n">
         <v>0.2709</v>
@@ -2092,13 +2092,13 @@
         <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3104</v>
+        <v>0.5641</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3358</v>
+        <v>0.535</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0253</v>
+        <v>0.0292</v>
       </c>
       <c r="V21" t="n">
         <v>-3.3418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3311</v>
+        <v>-3.4123</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7941</v>
+        <v>-3.0934</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.537</v>
+        <v>-0.319</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3246</v>
@@ -2170,13 +2170,13 @@
         <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8125</v>
+        <v>0.1063</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.424</v>
+        <v>0.2767</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3885</v>
+        <v>-0.1705</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>14.5772</v>
       </c>
       <c r="H23" t="n">
-        <v>9.878199999999998</v>
+        <v>9.8782</v>
       </c>
       <c r="I23" t="n">
         <v>4.6991</v>
@@ -2239,7 +2239,7 @@
         <v>1.835</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.850800000000001</v>
+        <v>-4.8508</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.5525</v>
@@ -2254,13 +2254,13 @@
         <v>4.559200000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1705</v>
+        <v>2.1704</v>
       </c>
       <c r="V23" t="n">
         <v>-3.4373</v>
       </c>
       <c r="W23" t="n">
-        <v>7.764200000000001</v>
+        <v>7.764199999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-11.2015</v>
